--- a/data/trans_bre/P19C03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C03-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 4,33</t>
+          <t>-6,86; 4,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 4,26</t>
+          <t>-5,96; 3,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 1,58</t>
+          <t>-9,11; 1,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,17; -1,18</t>
+          <t>-11,38; -1,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 12,62</t>
+          <t>-16,95; 13,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 16,8</t>
+          <t>-20,37; 15,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 6,51</t>
+          <t>-28,6; 6,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,92; -5,37</t>
+          <t>-40,53; -5,16</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 7,42</t>
+          <t>-2,14; 7,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 2,91</t>
+          <t>-6,24; 3,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 4,49</t>
+          <t>-3,9; 4,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 11,37</t>
+          <t>-0,63; 11,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 27,55</t>
+          <t>-6,64; 28,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 9,57</t>
+          <t>-18,22; 11,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 18,67</t>
+          <t>-13,63; 20,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 155,78</t>
+          <t>-3,59; 145,69</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 2,71</t>
+          <t>-9,14; 2,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 5,09</t>
+          <t>-5,64; 4,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 4,08</t>
+          <t>-7,05; 4,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 4,87</t>
+          <t>-16,24; 5,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 8,29</t>
+          <t>-23,11; 8,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 18,15</t>
+          <t>-17,07; 16,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 13,34</t>
+          <t>-19,57; 15,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,52; 20,3</t>
+          <t>-60,78; 22,69</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 5,24</t>
+          <t>-3,88; 5,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 3,87</t>
+          <t>-5,78; 3,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 3,2</t>
+          <t>-5,23; 3,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,91</t>
+          <t>-4,8; 2,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 20,17</t>
+          <t>-13,1; 19,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 14,64</t>
+          <t>-18,67; 11,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 14,97</t>
+          <t>-20,16; 17,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 20,24</t>
+          <t>-27,23; 17,28</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,75</t>
+          <t>-2,58; 2,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,21</t>
+          <t>-3,5; 1,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,14</t>
+          <t>-3,57; 1,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,76</t>
+          <t>-3,8; 4,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 9,06</t>
+          <t>-7,8; 9,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 4,17</t>
+          <t>-11,21; 5,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 4,17</t>
+          <t>-12,49; 4,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 24,24</t>
+          <t>-19,68; 25,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C03-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,58</t>
+          <t>-4,98</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-23,75%</t>
+          <t>-21,63%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 4,63</t>
+          <t>-7,45; 4,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 3,98</t>
+          <t>-5,43; 4,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 1,72</t>
+          <t>-9,17; 1,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,38; -1,1</t>
+          <t>-9,89; -0,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 13,58</t>
+          <t>-18,46; 14,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 15,2</t>
+          <t>-18,21; 18,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 6,19</t>
+          <t>-28,54; 5,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,53; -5,16</t>
+          <t>-37,19; -3,67</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,81</t>
+          <t>-1,86; 7,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 3,32</t>
+          <t>-6,34; 2,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 4,85</t>
+          <t>-3,65; 4,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 11,0</t>
+          <t>-2,29; 4,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 28,43</t>
+          <t>-6,07; 28,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 11,42</t>
+          <t>-18,03; 9,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 20,67</t>
+          <t>-12,69; 19,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 145,69</t>
+          <t>-12,35; 28,94</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-17,06%</t>
+          <t>-5,14%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 2,75</t>
+          <t>-8,96; 2,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 4,51</t>
+          <t>-5,74; 4,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 4,66</t>
+          <t>-7,71; 3,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 5,1</t>
+          <t>-5,81; 3,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 8,57</t>
+          <t>-23,37; 8,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 16,16</t>
+          <t>-17,16; 18,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 15,64</t>
+          <t>-21,32; 12,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,78; 22,69</t>
+          <t>-21,56; 16,04</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,68%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 5,06</t>
+          <t>-4,09; 5,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 3,12</t>
+          <t>-5,64; 3,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 3,63</t>
+          <t>-5,24; 3,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 2,48</t>
+          <t>-2,43; 3,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 19,9</t>
+          <t>-12,75; 20,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 11,44</t>
+          <t>-17,77; 12,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 17,36</t>
+          <t>-20,46; 16,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 17,28</t>
+          <t>-14,58; 29,34</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-2,79%</t>
+          <t>-4,16%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,75</t>
+          <t>-2,38; 2,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,52</t>
+          <t>-3,67; 1,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,15</t>
+          <t>-3,68; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,09</t>
+          <t>-2,78; 1,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 9,03</t>
+          <t>-7,27; 9,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 5,28</t>
+          <t>-11,64; 4,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 4,33</t>
+          <t>-12,85; 3,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 25,83</t>
+          <t>-13,84; 5,73</t>
         </is>
       </c>
     </row>
